--- a/data.mn/public/datasets/labor-participation-national.xlsx
+++ b/data.mn/public/datasets/labor-participation-national.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -434,273 +434,137 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1992</v>
+        <v>2009</v>
       </c>
       <c r="B2" t="n">
-        <v>75.8</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1993</v>
+        <v>2010</v>
       </c>
       <c r="B3" t="n">
-        <v>73.90000000000001</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1994</v>
+        <v>2011</v>
       </c>
       <c r="B4" t="n">
-        <v>71.8</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1995</v>
+        <v>2012</v>
       </c>
       <c r="B5" t="n">
-        <v>68.5</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1996</v>
+        <v>2013</v>
       </c>
       <c r="B6" t="n">
-        <v>68</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1997</v>
+        <v>2014</v>
       </c>
       <c r="B7" t="n">
-        <v>66.7</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1998</v>
+        <v>2015</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1999</v>
+        <v>2016</v>
       </c>
       <c r="B9" t="n">
-        <v>66.7</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2000</v>
+        <v>2017</v>
       </c>
       <c r="B10" t="n">
-        <v>62.9</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2001</v>
+        <v>2018</v>
       </c>
       <c r="B11" t="n">
-        <v>62.2</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2002</v>
+        <v>2019</v>
       </c>
       <c r="B12" t="n">
-        <v>62.6</v>
+        <v>62.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2003</v>
+        <v>2020</v>
       </c>
       <c r="B13" t="n">
-        <v>64.5</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2004</v>
+        <v>2021</v>
       </c>
       <c r="B14" t="n">
-        <v>64.40000000000001</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2005</v>
+        <v>2022</v>
       </c>
       <c r="B15" t="n">
-        <v>63.5</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2006</v>
+        <v>2023</v>
       </c>
       <c r="B16" t="n">
-        <v>64.40000000000001</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2007</v>
+        <v>2024</v>
       </c>
       <c r="B17" t="n">
-        <v>64.2</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2008</v>
+        <v>2025</v>
       </c>
       <c r="B18" t="n">
-        <v>63.5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>2009</v>
-      </c>
-      <c r="B19" t="n">
-        <v>61.4</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>2010</v>
-      </c>
-      <c r="B20" t="n">
-        <v>61.6</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>2011</v>
-      </c>
-      <c r="B21" t="n">
-        <v>62.5</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>2012</v>
-      </c>
-      <c r="B22" t="n">
-        <v>63.5</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B23" t="n">
-        <v>61.9</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>2014</v>
-      </c>
-      <c r="B24" t="n">
-        <v>62.1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B25" t="n">
-        <v>61.5</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>2016</v>
-      </c>
-      <c r="B26" t="n">
-        <v>60.5</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>2017</v>
-      </c>
-      <c r="B27" t="n">
-        <v>61.1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>2018</v>
-      </c>
-      <c r="B28" t="n">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>2019</v>
-      </c>
-      <c r="B29" t="n">
-        <v>62.8</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>2020</v>
-      </c>
-      <c r="B30" t="n">
-        <v>61.1</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>2021</v>
-      </c>
-      <c r="B31" t="n">
-        <v>59.1</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B32" t="n">
-        <v>60.3</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B33" t="n">
-        <v>59.5</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B34" t="n">
-        <v>61.3</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B35" t="n">
         <v>61.1</v>
       </c>
     </row>
